--- a/Teams/generated/MIXED TEAMS 2026 SUMMER - Contact Lists.xlsx
+++ b/Teams/generated/MIXED TEAMS 2026 SUMMER - Contact Lists.xlsx
@@ -500,7 +500,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 29 Mar 2026 10:45</t>
+          <t>Generated 29 Mar 2026 11:04</t>
         </is>
       </c>
     </row>
@@ -808,7 +808,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 29 Mar 2026 10:45</t>
+          <t>Generated 29 Mar 2026 11:04</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 29 Mar 2026 10:45</t>
+          <t>Generated 29 Mar 2026 11:04</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 29 Mar 2026 10:45</t>
+          <t>Generated 29 Mar 2026 11:04</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 29 Mar 2026 10:45</t>
+          <t>Generated 29 Mar 2026 11:04</t>
         </is>
       </c>
     </row>

--- a/Teams/generated/MIXED TEAMS 2026 SUMMER - Contact Lists.xlsx
+++ b/Teams/generated/MIXED TEAMS 2026 SUMMER - Contact Lists.xlsx
@@ -479,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -500,7 +500,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 29 Mar 2026 11:04</t>
+          <t>Generated 29 Mar 2026 11:10</t>
         </is>
       </c>
     </row>
@@ -751,7 +751,7 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>* Not Signed Up = exact name matched in club records, but no current paid 2026 membership was found.</t>
+          <t>* Not Signed Up = exact or resolved name matched in club records, but no current paid 2026 membership was found.</t>
         </is>
       </c>
     </row>
@@ -765,16 +765,32 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>*** Fuzzy = matched by the cautious fuzzy fallback after exact and override-based matching failed.</t>
+          <t>*** Override = resolved by an explicit override; this usually represents a typo or misspelling in the source data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>**** Nickname = resolved by a short-name or nickname rule; this may also represent a typo or misspelling in the source data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>***** Fuzzy = resolved by the cautious fuzzy fallback; this represents a typo or misspelling in the source data.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="7">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A16:F16"/>
     <mergeCell ref="A14:F14"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A17:F17"/>
+    <mergeCell ref="A18:F18"/>
     <mergeCell ref="A15:F15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -787,7 +803,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -808,7 +824,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 29 Mar 2026 11:04</t>
+          <t>Generated 29 Mar 2026 11:10</t>
         </is>
       </c>
     </row>
@@ -855,7 +871,11 @@
           <t>Sam Rush</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr"/>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Nickname</t>
+        </is>
+      </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
           <t>Senior</t>
@@ -879,7 +899,11 @@
           <t>Andy Roxburgh</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr"/>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Nickname</t>
+        </is>
+      </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
           <t>Not Signed Up</t>
@@ -1019,7 +1043,11 @@
           <t>Sue White</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr"/>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Nickname</t>
+        </is>
+      </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
           <t>Senior</t>
@@ -1043,7 +1071,11 @@
           <t>Tom Van Klavern</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr"/>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Override</t>
+        </is>
+      </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
           <t>Not Signed Up</t>
@@ -1087,7 +1119,7 @@
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>* Not Signed Up = exact name matched in club records, but no current paid 2026 membership was found.</t>
+          <t>* Not Signed Up = exact or resolved name matched in club records, but no current paid 2026 membership was found.</t>
         </is>
       </c>
     </row>
@@ -1101,16 +1133,32 @@
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>*** Fuzzy = matched by the cautious fuzzy fallback after exact and override-based matching failed.</t>
+          <t>*** Override = resolved by an explicit override; this usually represents a typo or misspelling in the source data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>**** Nickname = resolved by a short-name or nickname rule; this may also represent a typo or misspelling in the source data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>***** Fuzzy = resolved by the cautious fuzzy fallback; this represents a typo or misspelling in the source data.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="7">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A16:F16"/>
+    <mergeCell ref="A19:F19"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A17:F17"/>
+    <mergeCell ref="A18:F18"/>
     <mergeCell ref="A15:F15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1123,7 +1171,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1144,7 +1192,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 29 Mar 2026 11:04</t>
+          <t>Generated 29 Mar 2026 11:10</t>
         </is>
       </c>
     </row>
@@ -1215,7 +1263,11 @@
           <t>Alex Mach</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr"/>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Nickname</t>
+        </is>
+      </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
           <t>Not Signed Up</t>
@@ -1579,7 +1631,7 @@
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>* Not Signed Up = exact name matched in club records, but no current paid 2026 membership was found.</t>
+          <t>* Not Signed Up = exact or resolved name matched in club records, but no current paid 2026 membership was found.</t>
         </is>
       </c>
     </row>
@@ -1593,17 +1645,33 @@
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>*** Fuzzy = matched by the cautious fuzzy fallback after exact and override-based matching failed.</t>
+          <t>*** Override = resolved by an explicit override; this usually represents a typo or misspelling in the source data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>**** Nickname = resolved by a short-name or nickname rule; this may also represent a typo or misspelling in the source data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>***** Fuzzy = resolved by the cautious fuzzy fallback; this represents a typo or misspelling in the source data.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="7">
+    <mergeCell ref="A24:F24"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A23:F23"/>
     <mergeCell ref="A22:F22"/>
     <mergeCell ref="A21:F21"/>
+    <mergeCell ref="A25:F25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1615,7 +1683,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1636,7 +1704,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 29 Mar 2026 11:04</t>
+          <t>Generated 29 Mar 2026 11:10</t>
         </is>
       </c>
     </row>
@@ -1775,7 +1843,11 @@
           <t>Carol Ann Harrison</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr"/>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Override</t>
+        </is>
+      </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
           <t>Not Signed Up</t>
@@ -1875,7 +1947,11 @@
           <t>Jax S B</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr"/>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Override</t>
+        </is>
+      </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
           <t>Not Signed Up</t>
@@ -2171,7 +2247,7 @@
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>* Not Signed Up = exact name matched in club records, but no current paid 2026 membership was found.</t>
+          <t>* Not Signed Up = exact or resolved name matched in club records, but no current paid 2026 membership was found.</t>
         </is>
       </c>
     </row>
@@ -2185,16 +2261,32 @@
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>*** Fuzzy = matched by the cautious fuzzy fallback after exact and override-based matching failed.</t>
+          <t>*** Override = resolved by an explicit override; this usually represents a typo or misspelling in the source data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>**** Nickname = resolved by a short-name or nickname rule; this may also represent a typo or misspelling in the source data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>***** Fuzzy = resolved by the cautious fuzzy fallback; this represents a typo or misspelling in the source data.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="7">
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A28:F28"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A27:F27"/>
     <mergeCell ref="A26:F26"/>
+    <mergeCell ref="A29:F29"/>
     <mergeCell ref="A25:F25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2207,7 +2299,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2228,7 +2320,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 29 Mar 2026 11:04</t>
+          <t>Generated 29 Mar 2026 11:10</t>
         </is>
       </c>
     </row>
@@ -2591,7 +2683,11 @@
           <t>Jon Clackett</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr"/>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Nickname</t>
+        </is>
+      </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
           <t>Not Signed Up</t>
@@ -2639,7 +2735,11 @@
           <t>Matt Napper</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr"/>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Nickname</t>
+        </is>
+      </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
           <t>Senior</t>
@@ -2663,7 +2763,11 @@
           <t>Mo Clackett</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr"/>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>Nickname</t>
+        </is>
+      </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
           <t>Senior</t>
@@ -2851,7 +2955,7 @@
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>* Not Signed Up = exact name matched in club records, but no current paid 2026 membership was found.</t>
+          <t>* Not Signed Up = exact or resolved name matched in club records, but no current paid 2026 membership was found.</t>
         </is>
       </c>
     </row>
@@ -2865,14 +2969,30 @@
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>*** Fuzzy = matched by the cautious fuzzy fallback after exact and override-based matching failed.</t>
+          <t>*** Override = resolved by an explicit override; this usually represents a typo or misspelling in the source data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>**** Nickname = resolved by a short-name or nickname rule; this may also represent a typo or misspelling in the source data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>***** Fuzzy = resolved by the cautious fuzzy fallback; this represents a typo or misspelling in the source data.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="7">
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A33:F33"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A32:F32"/>
     <mergeCell ref="A31:F31"/>
     <mergeCell ref="A30:F30"/>
     <mergeCell ref="A29:F29"/>

--- a/Teams/generated/MIXED TEAMS 2026 SUMMER - Contact Lists.xlsx
+++ b/Teams/generated/MIXED TEAMS 2026 SUMMER - Contact Lists.xlsx
@@ -479,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -500,7 +500,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 29 Mar 2026 11:10</t>
+          <t>Generated 29 Mar 2026 11:15</t>
         </is>
       </c>
     </row>
@@ -765,28 +765,36 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>*** Override = resolved by an explicit override; this usually represents a typo or misspelling in the source data.</t>
+          <t>*** Best Fit = one row was chosen from several exact-name candidates using the best available contact evidence.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>**** Nickname = resolved by a short-name or nickname rule; this may also represent a typo or misspelling in the source data.</t>
+          <t>**** Override = resolved by an explicit override; this usually represents a typo or misspelling in the source data.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>***** Fuzzy = resolved by the cautious fuzzy fallback; this represents a typo or misspelling in the source data.</t>
+          <t>***** Nickname = resolved by a short-name or nickname rule; this may also represent a typo or misspelling in the source data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>****** Fuzzy = resolved by the cautious fuzzy fallback; this represents a typo or misspelling in the source data.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="8">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A16:F16"/>
+    <mergeCell ref="A19:F19"/>
     <mergeCell ref="A14:F14"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A17:F17"/>
@@ -803,7 +811,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -824,7 +832,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 29 Mar 2026 11:10</t>
+          <t>Generated 29 Mar 2026 11:15</t>
         </is>
       </c>
     </row>
@@ -1133,32 +1141,40 @@
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>*** Override = resolved by an explicit override; this usually represents a typo or misspelling in the source data.</t>
+          <t>*** Best Fit = one row was chosen from several exact-name candidates using the best available contact evidence.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>**** Nickname = resolved by a short-name or nickname rule; this may also represent a typo or misspelling in the source data.</t>
+          <t>**** Override = resolved by an explicit override; this usually represents a typo or misspelling in the source data.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>***** Fuzzy = resolved by the cautious fuzzy fallback; this represents a typo or misspelling in the source data.</t>
+          <t>***** Nickname = resolved by a short-name or nickname rule; this may also represent a typo or misspelling in the source data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>****** Fuzzy = resolved by the cautious fuzzy fallback; this represents a typo or misspelling in the source data.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="8">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A16:F16"/>
     <mergeCell ref="A19:F19"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A17:F17"/>
     <mergeCell ref="A18:F18"/>
+    <mergeCell ref="A20:F20"/>
     <mergeCell ref="A15:F15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1171,7 +1187,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1192,7 +1208,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 29 Mar 2026 11:10</t>
+          <t>Generated 29 Mar 2026 11:15</t>
         </is>
       </c>
     </row>
@@ -1645,31 +1661,39 @@
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>*** Override = resolved by an explicit override; this usually represents a typo or misspelling in the source data.</t>
+          <t>*** Best Fit = one row was chosen from several exact-name candidates using the best available contact evidence.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>**** Nickname = resolved by a short-name or nickname rule; this may also represent a typo or misspelling in the source data.</t>
+          <t>**** Override = resolved by an explicit override; this usually represents a typo or misspelling in the source data.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>***** Fuzzy = resolved by the cautious fuzzy fallback; this represents a typo or misspelling in the source data.</t>
+          <t>***** Nickname = resolved by a short-name or nickname rule; this may also represent a typo or misspelling in the source data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>****** Fuzzy = resolved by the cautious fuzzy fallback; this represents a typo or misspelling in the source data.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="8">
     <mergeCell ref="A24:F24"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A23:F23"/>
     <mergeCell ref="A22:F22"/>
+    <mergeCell ref="A26:F26"/>
     <mergeCell ref="A21:F21"/>
     <mergeCell ref="A25:F25"/>
   </mergeCells>
@@ -1683,7 +1707,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1704,7 +1728,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 29 Mar 2026 11:10</t>
+          <t>Generated 29 Mar 2026 11:15</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1947,11 @@
           <t>Harry McIntyre</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr"/>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Best Fit</t>
+        </is>
+      </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
           <t>Not Signed Up</t>
@@ -2261,31 +2289,39 @@
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>*** Override = resolved by an explicit override; this usually represents a typo or misspelling in the source data.</t>
+          <t>*** Best Fit = one row was chosen from several exact-name candidates using the best available contact evidence.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>**** Nickname = resolved by a short-name or nickname rule; this may also represent a typo or misspelling in the source data.</t>
+          <t>**** Override = resolved by an explicit override; this usually represents a typo or misspelling in the source data.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>***** Fuzzy = resolved by the cautious fuzzy fallback; this represents a typo or misspelling in the source data.</t>
+          <t>***** Nickname = resolved by a short-name or nickname rule; this may also represent a typo or misspelling in the source data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>****** Fuzzy = resolved by the cautious fuzzy fallback; this represents a typo or misspelling in the source data.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="8">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A28:F28"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A27:F27"/>
     <mergeCell ref="A26:F26"/>
+    <mergeCell ref="A30:F30"/>
     <mergeCell ref="A29:F29"/>
     <mergeCell ref="A25:F25"/>
   </mergeCells>
@@ -2299,7 +2335,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2320,7 +2356,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 29 Mar 2026 11:10</t>
+          <t>Generated 29 Mar 2026 11:15</t>
         </is>
       </c>
     </row>
@@ -2363,7 +2399,11 @@
           <t>Alistair Jones</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr"/>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Best Fit</t>
+        </is>
+      </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
           <t>Not Signed Up</t>
@@ -2659,7 +2699,11 @@
           <t>Joan McCrossan</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr"/>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>Best Fit</t>
+        </is>
+      </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
           <t>Not Signed Up</t>
@@ -2969,31 +3013,39 @@
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>*** Override = resolved by an explicit override; this usually represents a typo or misspelling in the source data.</t>
+          <t>*** Best Fit = one row was chosen from several exact-name candidates using the best available contact evidence.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>**** Nickname = resolved by a short-name or nickname rule; this may also represent a typo or misspelling in the source data.</t>
+          <t>**** Override = resolved by an explicit override; this usually represents a typo or misspelling in the source data.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>***** Fuzzy = resolved by the cautious fuzzy fallback; this represents a typo or misspelling in the source data.</t>
+          <t>***** Nickname = resolved by a short-name or nickname rule; this may also represent a typo or misspelling in the source data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>****** Fuzzy = resolved by the cautious fuzzy fallback; this represents a typo or misspelling in the source data.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="8">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A33:F33"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A32:F32"/>
     <mergeCell ref="A31:F31"/>
+    <mergeCell ref="A34:F34"/>
     <mergeCell ref="A30:F30"/>
     <mergeCell ref="A29:F29"/>
   </mergeCells>

--- a/Teams/generated/MIXED TEAMS 2026 SUMMER - Contact Lists.xlsx
+++ b/Teams/generated/MIXED TEAMS 2026 SUMMER - Contact Lists.xlsx
@@ -500,7 +500,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 29 Mar 2026 11:15</t>
+          <t>Generated 29 Mar 2026 12:50</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 29 Mar 2026 11:15</t>
+          <t>Generated 29 Mar 2026 12:50</t>
         </is>
       </c>
     </row>
@@ -1208,7 +1208,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 29 Mar 2026 11:15</t>
+          <t>Generated 29 Mar 2026 12:50</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 29 Mar 2026 11:15</t>
+          <t>Generated 29 Mar 2026 12:50</t>
         </is>
       </c>
     </row>
@@ -2356,7 +2356,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 29 Mar 2026 11:15</t>
+          <t>Generated 29 Mar 2026 12:50</t>
         </is>
       </c>
     </row>

--- a/Teams/generated/MIXED TEAMS 2026 SUMMER - Contact Lists.xlsx
+++ b/Teams/generated/MIXED TEAMS 2026 SUMMER - Contact Lists.xlsx
@@ -500,7 +500,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 29 Mar 2026 12:50</t>
+          <t>Generated 30 Mar 2026 14:35</t>
         </is>
       </c>
     </row>
@@ -579,12 +579,12 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>07962 260856</t>
+          <t>07962260856</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>jessica.palmer@flitepartners.com</t>
+          <t>JESSICA.PALMER@FLITEPARTNERS.COM</t>
         </is>
       </c>
     </row>
@@ -643,14 +643,26 @@
           <t>Jane Dow</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr"/>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Override</t>
+        </is>
+      </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>No Match</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="inlineStr"/>
-      <c r="F8" s="5" t="inlineStr"/>
+          <t>Senior</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>+447721967512</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>janeatimmis@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr"/>
@@ -832,7 +844,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 29 Mar 2026 12:50</t>
+          <t>Generated 30 Mar 2026 14:35</t>
         </is>
       </c>
     </row>
@@ -1208,7 +1220,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 29 Mar 2026 12:50</t>
+          <t>Generated 30 Mar 2026 14:35</t>
         </is>
       </c>
     </row>
@@ -1534,7 +1546,7 @@
       <c r="C15" s="5" t="inlineStr"/>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>Not Signed Up</t>
+          <t>Senior</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -1728,7 +1740,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 29 Mar 2026 12:50</t>
+          <t>Generated 30 Mar 2026 14:35</t>
         </is>
       </c>
     </row>
@@ -1833,8 +1845,16 @@
           <t>Not Signed Up</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr"/>
-      <c r="F6" s="5" t="inlineStr"/>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>07870 889889</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>georgenicolaidis@yahoo.co.uk</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr"/>
@@ -2356,7 +2376,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 29 Mar 2026 12:50</t>
+          <t>Generated 30 Mar 2026 14:35</t>
         </is>
       </c>
     </row>

--- a/Teams/generated/MIXED TEAMS 2026 SUMMER - Contact Lists.xlsx
+++ b/Teams/generated/MIXED TEAMS 2026 SUMMER - Contact Lists.xlsx
@@ -500,7 +500,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 30 Mar 2026 14:35</t>
+          <t>Generated 31 Mar 2026 15:53</t>
         </is>
       </c>
     </row>
@@ -844,7 +844,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 30 Mar 2026 14:35</t>
+          <t>Generated 31 Mar 2026 15:53</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1220,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 30 Mar 2026 14:35</t>
+          <t>Generated 31 Mar 2026 15:53</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 30 Mar 2026 14:35</t>
+          <t>Generated 31 Mar 2026 15:53</t>
         </is>
       </c>
     </row>
@@ -2376,7 +2376,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 30 Mar 2026 14:35</t>
+          <t>Generated 31 Mar 2026 15:53</t>
         </is>
       </c>
     </row>

--- a/Teams/generated/MIXED TEAMS 2026 SUMMER - Contact Lists.xlsx
+++ b/Teams/generated/MIXED TEAMS 2026 SUMMER - Contact Lists.xlsx
@@ -108,10 +108,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -479,350 +479,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="34" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Avondale Tennis Club | MIXED TEAMS 2026 Summer | A Squad</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Generated 31 Mar 2026 15:53</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>Captain</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>Match</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>Phone</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>Mark Elliott</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr"/>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>Not Signed Up</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>07842970820</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>m.k.m.s.elliott@hotmail.co.uk</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr"/>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>Amy Palmer</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr"/>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>Not Signed Up</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>07962260856</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>JESSICA.PALMER@FLITEPARTNERS.COM</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr"/>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>Ben Martin</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr"/>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>Not Signed Up</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>07867 585811</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>martin.ben40000@gmail.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr"/>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>David Pharo</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr"/>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>Not Signed Up</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>07974395880</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>david.pharo@aon.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr"/>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>Jane Dow</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>Override</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>Senior</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>+447721967512</t>
-        </is>
-      </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>janeatimmis@gmail.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr"/>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>Jane Vincent</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr"/>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>Not Signed Up</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>07787 824330</t>
-        </is>
-      </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>thevincents365@gmail.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr"/>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>Leila Warwick</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr"/>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>Not Signed Up</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>07973 684940</t>
-        </is>
-      </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>leilawarwick@me.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr"/>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>Paul Kemsley</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr"/>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>Not Signed Up</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>07747 105459</t>
-        </is>
-      </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>paul_kemsley@hotmail.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr"/>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>Peter Grant</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr"/>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>Senior</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>07736 252655</t>
-        </is>
-      </c>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>petergrant471@gmail.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>* Not Signed Up = exact or resolved name matched in club records, but no current paid 2026 membership was found.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>** No Match = no unique exact-name match was found in current club member/contact records.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>*** Best Fit = one row was chosen from several exact-name candidates using the best available contact evidence.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>**** Override = resolved by an explicit override; this usually represents a typo or misspelling in the source data.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>***** Nickname = resolved by a short-name or nickname rule; this may also represent a typo or misspelling in the source data.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>****** Fuzzy = resolved by the cautious fuzzy fallback; this represents a typo or misspelling in the source data.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A16:F16"/>
-    <mergeCell ref="A19:F19"/>
-    <mergeCell ref="A14:F14"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A17:F17"/>
-    <mergeCell ref="A18:F18"/>
-    <mergeCell ref="A15:F15"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -837,14 +493,14 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Avondale Tennis Club | MIXED TEAMS 2026 Summer | B Squad</t>
+          <t>Avondale Tennis Club | MIXED TEAMS 2026 Summer | A Squad</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 31 Mar 2026 15:53</t>
+          <t>Generated 01 Apr 2026 09:52</t>
         </is>
       </c>
     </row>
@@ -888,27 +544,23 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Sam Rush</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>Nickname</t>
-        </is>
-      </c>
+          <t>Mark Elliott</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr"/>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>Senior</t>
+          <t>Not Signed Up</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>07765 164044</t>
+          <t>07842970820</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>samrush336@gmail.com</t>
+          <t>m.k.m.s.elliott@hotmail.co.uk</t>
         </is>
       </c>
     </row>
@@ -916,14 +568,10 @@
       <c r="A5" s="5" t="inlineStr"/>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Andy Roxburgh</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>Nickname</t>
-        </is>
-      </c>
+          <t>Amy Palmer</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr"/>
       <c r="D5" s="5" t="inlineStr">
         <is>
           <t>Not Signed Up</t>
@@ -931,12 +579,12 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>07919459390</t>
+          <t>07962 260856</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>andy@roxburgh.je</t>
+          <t>jessica.palmer@flitepartners.com</t>
         </is>
       </c>
     </row>
@@ -944,23 +592,23 @@
       <c r="A6" s="5" t="inlineStr"/>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Cath Pearson</t>
+          <t>Ben Martin</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr"/>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Senior</t>
+          <t>Not Signed Up</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>07803 177572</t>
+          <t>07867 585811</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>cath.pearson@ntlworld.com</t>
+          <t>martin.ben40000@gmail.com</t>
         </is>
       </c>
     </row>
@@ -968,39 +616,51 @@
       <c r="A7" s="5" t="inlineStr"/>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Charlene Jacobs</t>
+          <t>David Pharo</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr"/>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>No Match</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr"/>
-      <c r="F7" s="5" t="inlineStr"/>
+          <t>Not Signed Up</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>07974395880</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>david.pharo@aon.com</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr"/>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Richard Longworth</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr"/>
+          <t>Jane Dow</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Override</t>
+        </is>
+      </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Not Signed Up</t>
+          <t>Senior</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>07508833898</t>
+          <t>+447721967512</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>rickieboy1@hotmail.com</t>
+          <t>janeatimmis@gmail.com</t>
         </is>
       </c>
     </row>
@@ -1008,7 +668,7 @@
       <c r="A9" s="5" t="inlineStr"/>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Rob Bozier</t>
+          <t>Jane Vincent</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr"/>
@@ -1019,12 +679,12 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>07969556875</t>
+          <t>07787 824330</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>robertbozier@yahoo.co.uk</t>
+          <t>thevincents365@gmail.com</t>
         </is>
       </c>
     </row>
@@ -1032,27 +692,23 @@
       <c r="A10" s="5" t="inlineStr"/>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Santu Asp</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>Fuzzy</t>
-        </is>
-      </c>
+          <t>Leila Warwick</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr"/>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Senior</t>
+          <t>Not Signed Up</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>07717 151014</t>
+          <t>No Consent</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>santtu.asp@gmail.com</t>
+          <t>No Consent</t>
         </is>
       </c>
     </row>
@@ -1060,27 +716,23 @@
       <c r="A11" s="5" t="inlineStr"/>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Sue White</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>Nickname</t>
-        </is>
-      </c>
+          <t>Paul Kemsley</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr"/>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>Senior</t>
+          <t>Not Signed Up</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>01256 893013</t>
+          <t>No Consent</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>susan582009@hotmail.co.uk</t>
+          <t>No Consent</t>
         </is>
       </c>
     </row>
@@ -1088,6 +740,362 @@
       <c r="A12" s="5" t="inlineStr"/>
       <c r="B12" s="5" t="inlineStr">
         <is>
+          <t>Peter Grant</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr"/>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>07736 252655</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>petergrant471@gmail.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>* Not Signed Up = exact or resolved name matched in club records, but no current paid 2026 membership was found.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>** No Match = no unique exact-name match was found in current club member/contact records.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>*** Best Fit = one row was chosen from several exact-name candidates using the best available contact evidence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>**** Override = resolved by an explicit override; this usually represents a typo or misspelling in the source data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>***** Nickname = resolved by a short-name or nickname rule; this may also represent a typo or misspelling in the source data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>****** Fuzzy = resolved by the cautious fuzzy fallback; this represents a typo or misspelling in the source data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>******* No Consent = the current contact record does not allow contact details to be shared, so phone and email are withheld.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A16:F16"/>
+    <mergeCell ref="A19:F19"/>
+    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A17:F17"/>
+    <mergeCell ref="A18:F18"/>
+    <mergeCell ref="A20:F20"/>
+    <mergeCell ref="A15:F15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Avondale Tennis Club | MIXED TEAMS 2026 Summer | B Squad</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Generated 01 Apr 2026 09:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Captain</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Match</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Sam Rush</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Nickname</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>No Consent</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>No Consent</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr"/>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Andy Roxburgh</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Nickname</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Not Signed Up</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>07919459390</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>andy@roxburgh.je</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr"/>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Cath Pearson</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr"/>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>07803 177572</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>cath.pearson@ntlworld.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr"/>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Charlene Jacobs</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr"/>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>No Match</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr"/>
+      <c r="F7" s="5" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr"/>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Richard Longworth</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr"/>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>Not Signed Up</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>07508833898</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>rickieboy1@hotmail.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr"/>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Rob Bozier</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr"/>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>Not Signed Up</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>No Consent</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>No Consent</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr"/>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Santu Asp</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Fuzzy</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>No Consent</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>No Consent</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr"/>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Sue White</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Nickname</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>No Consent</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>No Consent</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr"/>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
           <t>Tom Van Klavern</t>
         </is>
       </c>
@@ -1103,12 +1111,12 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>07502 285635</t>
+          <t>No Consent</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>tvk24@hotmail.co.uk</t>
+          <t>No Consent</t>
         </is>
       </c>
     </row>
@@ -1178,8 +1186,15 @@
         </is>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>******* No Consent = the current contact record does not allow contact details to be shared, so phone and email are withheld.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A16:F16"/>
     <mergeCell ref="A19:F19"/>
@@ -1187,6 +1202,7 @@
     <mergeCell ref="A17:F17"/>
     <mergeCell ref="A18:F18"/>
     <mergeCell ref="A20:F20"/>
+    <mergeCell ref="A21:F21"/>
     <mergeCell ref="A15:F15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1199,7 +1215,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1220,7 +1236,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 31 Mar 2026 15:53</t>
+          <t>Generated 01 Apr 2026 09:52</t>
         </is>
       </c>
     </row>
@@ -1275,12 +1291,12 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>07765 140012</t>
+          <t>No Consent</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>fran.999.jones@gmail.com</t>
+          <t>No Consent</t>
         </is>
       </c>
     </row>
@@ -1303,12 +1319,12 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>07724505363</t>
+          <t>No Consent</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>martyna.mach@gmail.com</t>
+          <t>No Consent</t>
         </is>
       </c>
     </row>
@@ -1698,12 +1714,20 @@
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>******* No Consent = the current contact record does not allow contact details to be shared, so phone and email are withheld.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="A24:F24"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A23:F23"/>
+    <mergeCell ref="A27:F27"/>
     <mergeCell ref="A22:F22"/>
     <mergeCell ref="A26:F26"/>
     <mergeCell ref="A21:F21"/>
@@ -1719,7 +1743,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1740,7 +1764,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 31 Mar 2026 15:53</t>
+          <t>Generated 01 Apr 2026 09:52</t>
         </is>
       </c>
     </row>
@@ -1819,12 +1843,12 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>07568 560257</t>
+          <t>No Consent</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>alex.katon@hotmail.com</t>
+          <t>No Consent</t>
         </is>
       </c>
     </row>
@@ -1847,12 +1871,12 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>07870 889889</t>
+          <t>No Consent</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>georgenicolaidis@yahoo.co.uk</t>
+          <t>No Consent</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1895,12 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>07306128175</t>
+          <t>No Consent</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>kerryandian@hotmail.com</t>
+          <t>No Consent</t>
         </is>
       </c>
     </row>
@@ -1979,12 +2003,12 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>07943603272</t>
+          <t>No Consent</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>harrymcintyre68@gmail.com</t>
+          <t>No Consent</t>
         </is>
       </c>
     </row>
@@ -2031,12 +2055,12 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>07962260856</t>
+          <t>No Consent</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>JESSICA.PALMER@FLITEPARTNERS.COM</t>
+          <t>No Consent</t>
         </is>
       </c>
     </row>
@@ -2055,12 +2079,12 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>7733247756</t>
+          <t>No Consent</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>jrvsemail@gmail.com</t>
+          <t>No Consent</t>
         </is>
       </c>
     </row>
@@ -2107,12 +2131,12 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>07769867559</t>
+          <t>No Consent</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>liz.gruenstern@gmail.com</t>
+          <t>No Consent</t>
         </is>
       </c>
     </row>
@@ -2159,12 +2183,12 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>07789394309</t>
+          <t>No Consent</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>n.fisher3@ntlworld.com</t>
+          <t>No Consent</t>
         </is>
       </c>
     </row>
@@ -2334,12 +2358,20 @@
         </is>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>******* No Consent = the current contact record does not allow contact details to be shared, so phone and email are withheld.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A28:F28"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A27:F27"/>
+    <mergeCell ref="A31:F31"/>
     <mergeCell ref="A26:F26"/>
     <mergeCell ref="A30:F30"/>
     <mergeCell ref="A29:F29"/>
@@ -2355,7 +2387,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2376,7 +2408,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 31 Mar 2026 15:53</t>
+          <t>Generated 01 Apr 2026 09:52</t>
         </is>
       </c>
     </row>
@@ -2431,12 +2463,12 @@
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>07741319024</t>
+          <t>No Consent</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>alistair@badmintonwycombe.co.uk</t>
+          <t>No Consent</t>
         </is>
       </c>
     </row>
@@ -2459,12 +2491,12 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>07825285272</t>
+          <t>No Consent</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>andy.d.mcelligott@gmail.com</t>
+          <t>No Consent</t>
         </is>
       </c>
     </row>
@@ -2651,12 +2683,12 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>07412335134</t>
+          <t>No Consent</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>jcholerton@gmail.com</t>
+          <t>No Consent</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2815,12 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>07711 603036</t>
+          <t>No Consent</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>lizzylong1@btinternet.com</t>
+          <t>No Consent</t>
         </is>
       </c>
     </row>
@@ -2839,12 +2871,12 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>07703 196204</t>
+          <t>No Consent</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>moclackett@gmail.com</t>
+          <t>No Consent</t>
         </is>
       </c>
     </row>
@@ -3058,14 +3090,22 @@
         </is>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>******* No Consent = the current contact record does not allow contact details to be shared, so phone and email are withheld.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A33:F33"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A32:F32"/>
     <mergeCell ref="A31:F31"/>
     <mergeCell ref="A34:F34"/>
+    <mergeCell ref="A35:F35"/>
     <mergeCell ref="A30:F30"/>
     <mergeCell ref="A29:F29"/>
   </mergeCells>

--- a/Teams/generated/MIXED TEAMS 2026 SUMMER - Contact Lists.xlsx
+++ b/Teams/generated/MIXED TEAMS 2026 SUMMER - Contact Lists.xlsx
@@ -43,7 +43,7 @@
     </font>
     <font>
       <i val="1"/>
-      <color rgb="006B7280"/>
+      <color rgb="001F1F1F"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -479,15 +479,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -500,7 +501,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 01 Apr 2026 09:52</t>
+          <t>Generated 02 Apr 2026 11:51</t>
         </is>
       </c>
     </row>
@@ -517,22 +518,27 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Consent</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
           <t>Match</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>Phone</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>Email</t>
         </is>
       </c>
     </row>
@@ -547,10 +553,14 @@
           <t>Mark Elliott</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr"/>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Not Signed Up</t>
+        </is>
+      </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>Not Signed Up</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
@@ -563,6 +573,7 @@
           <t>m.k.m.s.elliott@hotmail.co.uk</t>
         </is>
       </c>
+      <c r="G4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr"/>
@@ -571,22 +582,30 @@
           <t>Amy Palmer</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr"/>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Not Signed Up</t>
+        </is>
+      </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>Not Signed Up</t>
+          <t>Self: Yes
+Parent: No</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>07962 260856</t>
+          <t>Self: 07962 260856
+Parent: 07962260856</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>jessica.palmer@flitepartners.com</t>
-        </is>
-      </c>
+          <t>Self: jessica.palmer@flitepartners.com
+Parent: JESSICA.PALMER@FLITEPARTNERS.COM</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr"/>
@@ -595,10 +614,14 @@
           <t>Ben Martin</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr"/>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Not Signed Up</t>
+        </is>
+      </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Not Signed Up</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -611,6 +634,7 @@
           <t>martin.ben40000@gmail.com</t>
         </is>
       </c>
+      <c r="G6" s="5" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr"/>
@@ -619,10 +643,14 @@
           <t>David Pharo</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr"/>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Not Signed Up</t>
+        </is>
+      </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>Not Signed Up</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -635,6 +663,7 @@
           <t>david.pharo@aon.com</t>
         </is>
       </c>
+      <c r="G7" s="5" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr"/>
@@ -645,22 +674,27 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
+          <t>Senior</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>+447721967512</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>janeatimmis@gmail.com</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
           <t>Override</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>Senior</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>+447721967512</t>
-        </is>
-      </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>janeatimmis@gmail.com</t>
         </is>
       </c>
     </row>
@@ -671,10 +705,14 @@
           <t>Jane Vincent</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr"/>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Not Signed Up</t>
+        </is>
+      </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>Not Signed Up</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -687,6 +725,7 @@
           <t>thevincents365@gmail.com</t>
         </is>
       </c>
+      <c r="G9" s="5" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr"/>
@@ -695,22 +734,27 @@
           <t>Leila Warwick</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr"/>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Not Signed Up</t>
+        </is>
+      </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Not Signed Up</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>No Consent</t>
+          <t>07973 684940</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>No Consent</t>
-        </is>
-      </c>
+          <t>leilawarwick@me.com</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr"/>
@@ -719,22 +763,27 @@
           <t>Paul Kemsley</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr"/>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Not Signed Up</t>
+        </is>
+      </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>Not Signed Up</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>No Consent</t>
+          <t>07747 105459</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>No Consent</t>
-        </is>
-      </c>
+          <t>paul_kemsley@hotmail.com</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr"/>
@@ -743,10 +792,14 @@
           <t>Peter Grant</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr"/>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Senior</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -759,67 +812,68 @@
           <t>petergrant471@gmail.com</t>
         </is>
       </c>
+      <c r="G12" s="5" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>* Not Signed Up = exact or resolved name matched in club records, but no current paid 2026 membership was found.</t>
+          <t>* Consent: No means the captain may use the phone/email for team management, but may not pass it on to anyone else.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>** No Match = no unique exact-name match was found in current club member/contact records.</t>
+          <t>** Not Signed Up = no current membership was found.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>*** Best Fit = one row was chosen from several exact-name candidates using the best available contact evidence.</t>
+          <t>*** No Match = no unique exact-name match was found in current club member/contact records.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>**** Override = resolved by an explicit override; this usually represents a typo or misspelling in the source data.</t>
+          <t>**** Best Fit = one row was chosen from several exact-name candidates using the best available contact evidence.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>***** Nickname = resolved by a short-name or nickname rule; this may also represent a typo or misspelling in the source data.</t>
+          <t>***** Override = resolved by an explicit override; this usually represents a typo or misspelling in the source data.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>****** Fuzzy = resolved by the cautious fuzzy fallback; this represents a typo or misspelling in the source data.</t>
+          <t>****** Nickname = resolved by a short-name or nickname rule; this may also represent a typo or misspelling in the source data.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>******* No Consent = the current contact record does not allow contact details to be shared, so phone and email are withheld.</t>
+          <t>******* Fuzzy = resolved by the cautious fuzzy fallback; this represents a typo or misspelling in the source data.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A16:F16"/>
-    <mergeCell ref="A19:F19"/>
-    <mergeCell ref="A14:F14"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A17:F17"/>
-    <mergeCell ref="A18:F18"/>
-    <mergeCell ref="A20:F20"/>
-    <mergeCell ref="A15:F15"/>
+    <mergeCell ref="A14:G14"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A17:G17"/>
+    <mergeCell ref="A18:G18"/>
+    <mergeCell ref="A20:G20"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A16:G16"/>
+    <mergeCell ref="A15:G15"/>
+    <mergeCell ref="A19:G19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -831,15 +885,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -852,7 +907,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 01 Apr 2026 09:52</t>
+          <t>Generated 02 Apr 2026 11:51</t>
         </is>
       </c>
     </row>
@@ -869,22 +924,27 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Consent</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
           <t>Match</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>Phone</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>Email</t>
         </is>
       </c>
     </row>
@@ -901,22 +961,27 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
+          <t>Senior</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>07765 164044</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>samrush336@gmail.com</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
           <t>Nickname</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>Senior</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>No Consent</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>No Consent</t>
         </is>
       </c>
     </row>
@@ -929,22 +994,27 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
+          <t>Not Signed Up</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>07919459390</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>andy@roxburgh.je</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
           <t>Nickname</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>Not Signed Up</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>07919459390</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>andy@roxburgh.je</t>
         </is>
       </c>
     </row>
@@ -955,10 +1025,14 @@
           <t>Cath Pearson</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr"/>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Senior</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -971,6 +1045,7 @@
           <t>cath.pearson@ntlworld.com</t>
         </is>
       </c>
+      <c r="G6" s="5" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr"/>
@@ -979,14 +1054,27 @@
           <t>Charlene Jacobs</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr"/>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>No Match</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr"/>
-      <c r="F7" s="5" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>+447872314523</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>jacobscharlene@yahoo.com</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr"/>
@@ -995,10 +1083,14 @@
           <t>Richard Longworth</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr"/>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Not Signed Up</t>
+        </is>
+      </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Not Signed Up</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -1011,6 +1103,7 @@
           <t>rickieboy1@hotmail.com</t>
         </is>
       </c>
+      <c r="G8" s="5" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr"/>
@@ -1019,22 +1112,27 @@
           <t>Rob Bozier</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr"/>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Not Signed Up</t>
+        </is>
+      </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>Not Signed Up</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>No Consent</t>
+          <t>07969556875</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>No Consent</t>
-        </is>
-      </c>
+          <t>robertbozier@yahoo.co.uk</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr"/>
@@ -1045,22 +1143,27 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
+          <t>Senior</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>07717 151014</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>santtu.asp@gmail.com</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
           <t>Fuzzy</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>Senior</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>No Consent</t>
-        </is>
-      </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>No Consent</t>
         </is>
       </c>
     </row>
@@ -1073,22 +1176,27 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
+          <t>Senior</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>01256 893013</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>susan582009@hotmail.co.uk</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
           <t>Nickname</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>Senior</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>No Consent</t>
-        </is>
-      </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>No Consent</t>
         </is>
       </c>
     </row>
@@ -1101,22 +1209,27 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
+          <t>Not Signed Up</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>07502 285635</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>tvk24@hotmail.co.uk</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
           <t>Override</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>Not Signed Up</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>No Consent</t>
-        </is>
-      </c>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>No Consent</t>
         </is>
       </c>
     </row>
@@ -1127,10 +1240,14 @@
           <t>Wendy Day</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr"/>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>Senior</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -1143,67 +1260,68 @@
           <t>W_mudd@yahoo.com</t>
         </is>
       </c>
+      <c r="G13" s="5" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>* Not Signed Up = exact or resolved name matched in club records, but no current paid 2026 membership was found.</t>
+          <t>* Consent: No means the captain may use the phone/email for team management, but may not pass it on to anyone else.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>** No Match = no unique exact-name match was found in current club member/contact records.</t>
+          <t>** Not Signed Up = no current membership was found.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>*** Best Fit = one row was chosen from several exact-name candidates using the best available contact evidence.</t>
+          <t>*** No Match = no unique exact-name match was found in current club member/contact records.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>**** Override = resolved by an explicit override; this usually represents a typo or misspelling in the source data.</t>
+          <t>**** Best Fit = one row was chosen from several exact-name candidates using the best available contact evidence.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>***** Nickname = resolved by a short-name or nickname rule; this may also represent a typo or misspelling in the source data.</t>
+          <t>***** Override = resolved by an explicit override; this usually represents a typo or misspelling in the source data.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>****** Fuzzy = resolved by the cautious fuzzy fallback; this represents a typo or misspelling in the source data.</t>
+          <t>****** Nickname = resolved by a short-name or nickname rule; this may also represent a typo or misspelling in the source data.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>******* No Consent = the current contact record does not allow contact details to be shared, so phone and email are withheld.</t>
+          <t>******* Fuzzy = resolved by the cautious fuzzy fallback; this represents a typo or misspelling in the source data.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A16:F16"/>
-    <mergeCell ref="A19:F19"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A17:F17"/>
-    <mergeCell ref="A18:F18"/>
-    <mergeCell ref="A20:F20"/>
-    <mergeCell ref="A21:F21"/>
-    <mergeCell ref="A15:F15"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A17:G17"/>
+    <mergeCell ref="A18:G18"/>
+    <mergeCell ref="A21:G21"/>
+    <mergeCell ref="A20:G20"/>
+    <mergeCell ref="A16:G16"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A15:G15"/>
+    <mergeCell ref="A19:G19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1215,15 +1333,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -1236,7 +1355,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 01 Apr 2026 09:52</t>
+          <t>Generated 02 Apr 2026 11:51</t>
         </is>
       </c>
     </row>
@@ -1253,22 +1372,27 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Consent</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
           <t>Match</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>Phone</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>Email</t>
         </is>
       </c>
     </row>
@@ -1283,22 +1407,27 @@
           <t>Fran Jones</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr"/>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>Senior</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>No Consent</t>
+          <t>07765 140012</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>No Consent</t>
-        </is>
-      </c>
+          <t>fran.999.jones@gmail.com</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr"/>
@@ -1309,22 +1438,30 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
+          <t>Not Signed Up</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Self: No
+Parent: No</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>Self: 07724505363
+Parent: 07724505363</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>Self: martyna.mach@gmail.com
+Parent: martyna.mach@gmail.com</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
           <t>Nickname</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>Not Signed Up</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>No Consent</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>No Consent</t>
         </is>
       </c>
     </row>
@@ -1335,10 +1472,14 @@
           <t>Alexander Peacock</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr"/>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Young Adult</t>
+        </is>
+      </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Young Adult</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -1351,6 +1492,7 @@
           <t>peacock156@googlemail.com</t>
         </is>
       </c>
+      <c r="G6" s="5" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr"/>
@@ -1361,22 +1503,27 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
+          <t>Senior</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>07593 569268</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>alison.jameson@gmail.com</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
           <t>Fuzzy</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>Senior</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>07593 569268</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>alison.jameson@gmail.com</t>
         </is>
       </c>
     </row>
@@ -1387,10 +1534,14 @@
           <t>David Alston</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr"/>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Senior</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -1403,6 +1554,7 @@
           <t>alstondr@hotmail.com</t>
         </is>
       </c>
+      <c r="G8" s="5" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr"/>
@@ -1411,10 +1563,14 @@
           <t>Diane Doyle</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr"/>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>Senior</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -1427,6 +1583,7 @@
           <t>dianeldoyle@gmail.com</t>
         </is>
       </c>
+      <c r="G9" s="5" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr"/>
@@ -1435,10 +1592,14 @@
           <t>James Carlisle</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr"/>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Senior</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -1451,6 +1612,7 @@
           <t>jamescarli@hotmail.co.uk</t>
         </is>
       </c>
+      <c r="G10" s="5" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr"/>
@@ -1459,10 +1621,14 @@
           <t>Joanne Stanley</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr"/>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Not Signed Up</t>
+        </is>
+      </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>Not Signed Up</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -1475,6 +1641,7 @@
           <t>joanneecairns@hotmail.com</t>
         </is>
       </c>
+      <c r="G11" s="5" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr"/>
@@ -1483,10 +1650,14 @@
           <t>Kim Field</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr"/>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Senior</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -1499,6 +1670,7 @@
           <t>kimfield65@gmail.com</t>
         </is>
       </c>
+      <c r="G12" s="5" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr"/>
@@ -1509,22 +1681,27 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
+          <t>Not Signed Up</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>07887 522574</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>Lynnmckenzie@live.co.uk</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
           <t>Fuzzy</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>Not Signed Up</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>07887 522574</t>
-        </is>
-      </c>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t>Lynnmckenzie@live.co.uk</t>
         </is>
       </c>
     </row>
@@ -1535,10 +1712,14 @@
           <t>Mark Hill</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr"/>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Not Signed Up</t>
+        </is>
+      </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Not Signed Up</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -1551,6 +1732,7 @@
           <t>markyh20@gmail.com</t>
         </is>
       </c>
+      <c r="G14" s="5" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr"/>
@@ -1559,10 +1741,14 @@
           <t>Mike Thornley</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr"/>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>Senior</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -1575,6 +1761,7 @@
           <t>mike33lufc@gmail.com</t>
         </is>
       </c>
+      <c r="G15" s="5" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr"/>
@@ -1583,10 +1770,14 @@
           <t>Pauline Snell</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr"/>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Senior</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -1599,6 +1790,7 @@
           <t>psnell66@gmail.com</t>
         </is>
       </c>
+      <c r="G16" s="5" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr"/>
@@ -1607,10 +1799,14 @@
           <t>Peter Smith</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr"/>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Not Signed Up</t>
+        </is>
+      </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>Not Signed Up</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -1623,6 +1819,7 @@
           <t>Peterrcsmith@hotmail.co.uk</t>
         </is>
       </c>
+      <c r="G17" s="5" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr"/>
@@ -1631,10 +1828,14 @@
           <t>Stuart Aberdeen</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr"/>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Senior</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -1647,6 +1848,7 @@
           <t>stuaberdeen@live.co.uk</t>
         </is>
       </c>
+      <c r="G18" s="5" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr"/>
@@ -1655,10 +1857,14 @@
           <t>Tom Blake</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr"/>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Family</t>
+        </is>
+      </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>Family</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -1671,67 +1877,68 @@
           <t>t_blake@icloud.com</t>
         </is>
       </c>
+      <c r="G19" s="5" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>* Not Signed Up = exact or resolved name matched in club records, but no current paid 2026 membership was found.</t>
+          <t>* Consent: No means the captain may use the phone/email for team management, but may not pass it on to anyone else.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>** No Match = no unique exact-name match was found in current club member/contact records.</t>
+          <t>** Not Signed Up = no current membership was found.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>*** Best Fit = one row was chosen from several exact-name candidates using the best available contact evidence.</t>
+          <t>*** No Match = no unique exact-name match was found in current club member/contact records.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>**** Override = resolved by an explicit override; this usually represents a typo or misspelling in the source data.</t>
+          <t>**** Best Fit = one row was chosen from several exact-name candidates using the best available contact evidence.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>***** Nickname = resolved by a short-name or nickname rule; this may also represent a typo or misspelling in the source data.</t>
+          <t>***** Override = resolved by an explicit override; this usually represents a typo or misspelling in the source data.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>****** Fuzzy = resolved by the cautious fuzzy fallback; this represents a typo or misspelling in the source data.</t>
+          <t>****** Nickname = resolved by a short-name or nickname rule; this may also represent a typo or misspelling in the source data.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>******* No Consent = the current contact record does not allow contact details to be shared, so phone and email are withheld.</t>
+          <t>******* Fuzzy = resolved by the cautious fuzzy fallback; this represents a typo or misspelling in the source data.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="A24:F24"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A23:F23"/>
-    <mergeCell ref="A27:F27"/>
-    <mergeCell ref="A22:F22"/>
-    <mergeCell ref="A26:F26"/>
-    <mergeCell ref="A21:F21"/>
-    <mergeCell ref="A25:F25"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A27:G27"/>
+    <mergeCell ref="A21:G21"/>
+    <mergeCell ref="A22:G22"/>
+    <mergeCell ref="A26:G26"/>
+    <mergeCell ref="A24:G24"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A25:G25"/>
+    <mergeCell ref="A23:G23"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1743,15 +1950,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -1764,7 +1972,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 01 Apr 2026 09:52</t>
+          <t>Generated 02 Apr 2026 11:51</t>
         </is>
       </c>
     </row>
@@ -1781,22 +1989,27 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Consent</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
           <t>Match</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>Phone</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>Email</t>
         </is>
       </c>
     </row>
@@ -1811,10 +2024,14 @@
           <t>Juliet Worthington</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr"/>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>Senior</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
@@ -1827,6 +2044,7 @@
           <t>juliet_worthington@hotmail.com</t>
         </is>
       </c>
+      <c r="G4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr"/>
@@ -1835,22 +2053,27 @@
           <t>Alex katon</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr"/>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Not Signed Up</t>
+        </is>
+      </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>Not Signed Up</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>No Consent</t>
+          <t>07568 560257</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>No Consent</t>
-        </is>
-      </c>
+          <t>alex.katon@hotmail.com</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr"/>
@@ -1861,22 +2084,27 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
+          <t>Not Signed Up</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>07870 889889</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>georgenicolaidis@yahoo.co.uk</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
           <t>Fuzzy</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>Not Signed Up</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>No Consent</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>No Consent</t>
         </is>
       </c>
     </row>
@@ -1887,22 +2115,27 @@
           <t>Ben Hammond Duncan</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr"/>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Young Adult</t>
+        </is>
+      </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>Young Adult</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>No Consent</t>
+          <t>07306128175</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>No Consent</t>
-        </is>
-      </c>
+          <t>kerryandian@hotmail.com</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr"/>
@@ -1913,22 +2146,27 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
+          <t>Not Signed Up</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>07799624958</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>cah.dbf@gmail.com</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
           <t>Override</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>Not Signed Up</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>07799624958</t>
-        </is>
-      </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>cah.dbf@gmail.com</t>
         </is>
       </c>
     </row>
@@ -1939,10 +2177,14 @@
           <t>Claire Taylor</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr"/>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>Not Signed Up</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -1955,6 +2197,7 @@
           <t>clairechicago1@gmail.com</t>
         </is>
       </c>
+      <c r="G9" s="5" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr"/>
@@ -1965,22 +2208,27 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
+          <t>Not Signed Up</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>07999775732</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>gdhutchison@me.com</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
           <t>Fuzzy</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>Not Signed Up</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>07999775732</t>
-        </is>
-      </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>gdhutchison@me.com</t>
         </is>
       </c>
     </row>
@@ -1993,22 +2241,27 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
+          <t>Not Signed Up</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>07943603272</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>harrymcintyre68@gmail.com</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
           <t>Best Fit</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>Not Signed Up</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>No Consent</t>
-        </is>
-      </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>No Consent</t>
         </is>
       </c>
     </row>
@@ -2021,22 +2274,27 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
+          <t>Not Signed Up</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>07889433872</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>jaxsb1962@gmail.com</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
           <t>Override</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>Not Signed Up</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>07889433872</t>
-        </is>
-      </c>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>jaxsb1962@gmail.com</t>
         </is>
       </c>
     </row>
@@ -2047,22 +2305,27 @@
           <t>Jessica Palmer</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr"/>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Not Signed Up</t>
+        </is>
+      </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>Not Signed Up</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>No Consent</t>
+          <t>07962260856</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>No Consent</t>
-        </is>
-      </c>
+          <t>JESSICA.PALMER@FLITEPARTNERS.COM</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr"/>
@@ -2071,22 +2334,27 @@
           <t>Joel Villamayor</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr"/>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Not Signed Up</t>
+        </is>
+      </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Not Signed Up</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>No Consent</t>
+          <t>7733247756</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>No Consent</t>
-        </is>
-      </c>
+          <t>jrvsemail@gmail.com</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr"/>
@@ -2095,10 +2363,14 @@
           <t>Jonty Maston</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr"/>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Not Signed Up</t>
+        </is>
+      </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>Not Signed Up</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -2111,6 +2383,7 @@
           <t>j.maston@btinternet.com</t>
         </is>
       </c>
+      <c r="G15" s="5" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr"/>
@@ -2121,22 +2394,27 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
+          <t>Senior</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>07769867559</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>liz.gruenstern@gmail.com</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
           <t>Fuzzy</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="inlineStr">
-        <is>
-          <t>Senior</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>No Consent</t>
-        </is>
-      </c>
-      <c r="F16" s="5" t="inlineStr">
-        <is>
-          <t>No Consent</t>
         </is>
       </c>
     </row>
@@ -2149,22 +2427,27 @@
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
+          <t>Not Signed Up</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>07885719965</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>walanda@hotmail.com</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
           <t>Fuzzy</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>Not Signed Up</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>07885719965</t>
-        </is>
-      </c>
-      <c r="F17" s="5" t="inlineStr">
-        <is>
-          <t>walanda@hotmail.com</t>
         </is>
       </c>
     </row>
@@ -2175,22 +2458,27 @@
           <t>Nigel Fisher</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr"/>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Senior</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>No Consent</t>
+          <t>07789394309</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>No Consent</t>
-        </is>
-      </c>
+          <t>n.fisher3@ntlworld.com</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr"/>
@@ -2201,22 +2489,27 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
+          <t>Not Signed Up</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>07918696633</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>tippo74@gmail.com</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
           <t>Fuzzy</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t>Not Signed Up</t>
-        </is>
-      </c>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t>07918696633</t>
-        </is>
-      </c>
-      <c r="F19" s="5" t="inlineStr">
-        <is>
-          <t>tippo74@gmail.com</t>
         </is>
       </c>
     </row>
@@ -2227,10 +2520,14 @@
           <t>Roger Barnacle</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr"/>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>Not Signed Up</t>
+        </is>
+      </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Not Signed Up</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -2243,6 +2540,7 @@
           <t>rbarnacle1@gmail.com</t>
         </is>
       </c>
+      <c r="G20" s="5" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr"/>
@@ -2251,10 +2549,14 @@
           <t>Steve Short</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr"/>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>Senior</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -2267,6 +2569,7 @@
           <t>members.avondaleltc@gmail.com</t>
         </is>
       </c>
+      <c r="G21" s="5" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr"/>
@@ -2275,10 +2578,14 @@
           <t>Susan Gilchrist</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr"/>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>Senior</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -2291,6 +2598,7 @@
           <t>mrs.susan.gilchrist@gmail.com</t>
         </is>
       </c>
+      <c r="G22" s="5" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr"/>
@@ -2299,10 +2607,14 @@
           <t>Tim Read</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr"/>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Not Signed Up</t>
+        </is>
+      </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>Not Signed Up</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -2315,67 +2627,68 @@
           <t>t.read423@gmail.com</t>
         </is>
       </c>
+      <c r="G23" s="5" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>* Not Signed Up = exact or resolved name matched in club records, but no current paid 2026 membership was found.</t>
+          <t>* Consent: No means the captain may use the phone/email for team management, but may not pass it on to anyone else.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>** No Match = no unique exact-name match was found in current club member/contact records.</t>
+          <t>** Not Signed Up = no current membership was found.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>*** Best Fit = one row was chosen from several exact-name candidates using the best available contact evidence.</t>
+          <t>*** No Match = no unique exact-name match was found in current club member/contact records.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>**** Override = resolved by an explicit override; this usually represents a typo or misspelling in the source data.</t>
+          <t>**** Best Fit = one row was chosen from several exact-name candidates using the best available contact evidence.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>***** Nickname = resolved by a short-name or nickname rule; this may also represent a typo or misspelling in the source data.</t>
+          <t>***** Override = resolved by an explicit override; this usually represents a typo or misspelling in the source data.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>****** Fuzzy = resolved by the cautious fuzzy fallback; this represents a typo or misspelling in the source data.</t>
+          <t>****** Nickname = resolved by a short-name or nickname rule; this may also represent a typo or misspelling in the source data.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>******* No Consent = the current contact record does not allow contact details to be shared, so phone and email are withheld.</t>
+          <t>******* Fuzzy = resolved by the cautious fuzzy fallback; this represents a typo or misspelling in the source data.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A28:F28"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A27:F27"/>
-    <mergeCell ref="A31:F31"/>
-    <mergeCell ref="A26:F26"/>
-    <mergeCell ref="A30:F30"/>
-    <mergeCell ref="A29:F29"/>
-    <mergeCell ref="A25:F25"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A27:G27"/>
+    <mergeCell ref="A31:G31"/>
+    <mergeCell ref="A26:G26"/>
+    <mergeCell ref="A30:G30"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A29:G29"/>
+    <mergeCell ref="A25:G25"/>
+    <mergeCell ref="A28:G28"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2387,15 +2700,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -2408,7 +2722,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 01 Apr 2026 09:52</t>
+          <t>Generated 02 Apr 2026 11:51</t>
         </is>
       </c>
     </row>
@@ -2425,22 +2739,27 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Consent</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
           <t>Match</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>Phone</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>Email</t>
         </is>
       </c>
     </row>
@@ -2453,22 +2772,27 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
+          <t>Not Signed Up</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>07741319024</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>alistair@badmintonwycombe.co.uk</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
           <t>Best Fit</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>Not Signed Up</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>No Consent</t>
-        </is>
-      </c>
-      <c r="F4" s="5" t="inlineStr">
-        <is>
-          <t>No Consent</t>
         </is>
       </c>
     </row>
@@ -2481,22 +2805,27 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
+          <t>Not Signed Up</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>07825285272</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>andy.d.mcelligott@gmail.com</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
           <t>Fuzzy</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>Not Signed Up</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>No Consent</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>No Consent</t>
         </is>
       </c>
     </row>
@@ -2507,10 +2836,14 @@
           <t>Chris Ezra</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr"/>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Not Signed Up</t>
+        </is>
+      </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Not Signed Up</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -2523,6 +2856,7 @@
           <t>casabella@btinternet.com</t>
         </is>
       </c>
+      <c r="G6" s="5" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr"/>
@@ -2531,10 +2865,14 @@
           <t>Cliff Church</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr"/>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>Not Signed Up</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -2547,6 +2885,7 @@
           <t>cliffchurch@hotmail.com</t>
         </is>
       </c>
+      <c r="G7" s="5" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr"/>
@@ -2555,10 +2894,14 @@
           <t>David Fowler</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr"/>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Senior</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -2571,6 +2914,7 @@
           <t>davidrfowler@msn.com</t>
         </is>
       </c>
+      <c r="G8" s="5" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr"/>
@@ -2579,10 +2923,14 @@
           <t>Derek Carder</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr"/>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>Senior</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -2595,6 +2943,7 @@
           <t>derekcarder@rocketmail.com</t>
         </is>
       </c>
+      <c r="G9" s="5" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr"/>
@@ -2603,10 +2952,14 @@
           <t>Edward Woods</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr"/>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Senior</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -2619,6 +2972,7 @@
           <t>edwardanthonywoods@gmail.com</t>
         </is>
       </c>
+      <c r="G10" s="5" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr"/>
@@ -2627,10 +2981,14 @@
           <t>Georgina Riches</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr"/>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>Not Signed Up</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -2643,6 +3001,7 @@
           <t>fam.riches@btinternet.com</t>
         </is>
       </c>
+      <c r="G11" s="5" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr"/>
@@ -2651,10 +3010,14 @@
           <t>Graham Friel</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr"/>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Not Signed Up</t>
+        </is>
+      </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Not Signed Up</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -2667,6 +3030,7 @@
           <t>gt_friel@hotmail.com</t>
         </is>
       </c>
+      <c r="G12" s="5" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr"/>
@@ -2675,22 +3039,27 @@
           <t>James Cholerton</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr"/>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>Senior</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>No Consent</t>
+          <t>07412335134</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>No Consent</t>
-        </is>
-      </c>
+          <t>jcholerton@gmail.com</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr"/>
@@ -2699,10 +3068,14 @@
           <t>James Colpus</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr"/>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Not Signed Up</t>
+        </is>
+      </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Not Signed Up</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -2715,6 +3088,7 @@
           <t>colpus9@gmail.com</t>
         </is>
       </c>
+      <c r="G14" s="5" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr"/>
@@ -2725,22 +3099,27 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
+          <t>Senior</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>07845 144977</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>jillian.penton@virginmedia.com</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
           <t>Fuzzy</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>Senior</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>07845 144977</t>
-        </is>
-      </c>
-      <c r="F15" s="5" t="inlineStr">
-        <is>
-          <t>jillian.penton@virginmedia.com</t>
         </is>
       </c>
     </row>
@@ -2753,22 +3132,27 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
+          <t>Not Signed Up</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>07739708728</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>jemccrossan@aol.com</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
           <t>Best Fit</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="inlineStr">
-        <is>
-          <t>Not Signed Up</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>07739708728</t>
-        </is>
-      </c>
-      <c r="F16" s="5" t="inlineStr">
-        <is>
-          <t>jemccrossan@aol.com</t>
         </is>
       </c>
     </row>
@@ -2781,22 +3165,27 @@
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
+          <t>Not Signed Up</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>07799 435600</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>jonathanclackett02@gmail.com</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
           <t>Nickname</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>Not Signed Up</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>07799 435600</t>
-        </is>
-      </c>
-      <c r="F17" s="5" t="inlineStr">
-        <is>
-          <t>jonathanclackett02@gmail.com</t>
         </is>
       </c>
     </row>
@@ -2807,22 +3196,27 @@
           <t>Liz Long</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr"/>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Not Signed Up</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>No Consent</t>
+          <t>07711 603036</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>No Consent</t>
-        </is>
-      </c>
+          <t>lizzylong1@btinternet.com</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr"/>
@@ -2833,22 +3227,27 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
+          <t>Senior</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>+447974699847</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>mattnapper2@gmail.com</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
           <t>Nickname</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t>Senior</t>
-        </is>
-      </c>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t>+447974699847</t>
-        </is>
-      </c>
-      <c r="F19" s="5" t="inlineStr">
-        <is>
-          <t>mattnapper2@gmail.com</t>
         </is>
       </c>
     </row>
@@ -2861,22 +3260,27 @@
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
+          <t>Senior</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>07703 196204</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>moclackett@gmail.com</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
           <t>Nickname</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="inlineStr">
-        <is>
-          <t>Senior</t>
-        </is>
-      </c>
-      <c r="E20" s="5" t="inlineStr">
-        <is>
-          <t>No Consent</t>
-        </is>
-      </c>
-      <c r="F20" s="5" t="inlineStr">
-        <is>
-          <t>No Consent</t>
         </is>
       </c>
     </row>
@@ -2887,10 +3291,14 @@
           <t>Paul Hampshire</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr"/>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>Senior</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -2903,6 +3311,7 @@
           <t>paul.hampshire63@hotmail.com</t>
         </is>
       </c>
+      <c r="G21" s="5" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr"/>
@@ -2911,10 +3320,14 @@
           <t>Paul Treacy</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr"/>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>Senior</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -2927,6 +3340,7 @@
           <t>paultreacy01@gmail.com</t>
         </is>
       </c>
+      <c r="G22" s="5" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr"/>
@@ -2935,10 +3349,14 @@
           <t>Richard Vallis</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr"/>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>Senior</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -2951,6 +3369,7 @@
           <t>Rbvallis@gmail.com</t>
         </is>
       </c>
+      <c r="G23" s="5" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr"/>
@@ -2959,10 +3378,14 @@
           <t>Sally Charlton</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr"/>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>Senior</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -2975,6 +3398,7 @@
           <t>sallycharlton22@btinternet.com</t>
         </is>
       </c>
+      <c r="G24" s="5" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr"/>
@@ -2983,10 +3407,14 @@
           <t>Sian Thomas</t>
         </is>
       </c>
-      <c r="C25" s="5" t="inlineStr"/>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>Senior</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -2999,6 +3427,7 @@
           <t>siannie.thomas@icloud.com</t>
         </is>
       </c>
+      <c r="G25" s="5" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr"/>
@@ -3007,10 +3436,14 @@
           <t>Stuart Lamb</t>
         </is>
       </c>
-      <c r="C26" s="5" t="inlineStr"/>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>Not Signed Up</t>
+        </is>
+      </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>Not Signed Up</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -3023,6 +3456,7 @@
           <t>stuart.lamb@hotmail.co.uk</t>
         </is>
       </c>
+      <c r="G26" s="5" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr"/>
@@ -3031,10 +3465,14 @@
           <t>Val Talbot</t>
         </is>
       </c>
-      <c r="C27" s="5" t="inlineStr"/>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>Senior</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -3047,67 +3485,68 @@
           <t>valerie.talbot@ntlworld.com</t>
         </is>
       </c>
+      <c r="G27" s="5" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>* Not Signed Up = exact or resolved name matched in club records, but no current paid 2026 membership was found.</t>
+          <t>* Consent: No means the captain may use the phone/email for team management, but may not pass it on to anyone else.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>** No Match = no unique exact-name match was found in current club member/contact records.</t>
+          <t>** Not Signed Up = no current membership was found.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>*** Best Fit = one row was chosen from several exact-name candidates using the best available contact evidence.</t>
+          <t>*** No Match = no unique exact-name match was found in current club member/contact records.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>**** Override = resolved by an explicit override; this usually represents a typo or misspelling in the source data.</t>
+          <t>**** Best Fit = one row was chosen from several exact-name candidates using the best available contact evidence.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>***** Nickname = resolved by a short-name or nickname rule; this may also represent a typo or misspelling in the source data.</t>
+          <t>***** Override = resolved by an explicit override; this usually represents a typo or misspelling in the source data.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>****** Fuzzy = resolved by the cautious fuzzy fallback; this represents a typo or misspelling in the source data.</t>
+          <t>****** Nickname = resolved by a short-name or nickname rule; this may also represent a typo or misspelling in the source data.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>******* No Consent = the current contact record does not allow contact details to be shared, so phone and email are withheld.</t>
+          <t>******* Fuzzy = resolved by the cautious fuzzy fallback; this represents a typo or misspelling in the source data.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A33:F33"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A32:F32"/>
-    <mergeCell ref="A31:F31"/>
-    <mergeCell ref="A34:F34"/>
-    <mergeCell ref="A35:F35"/>
-    <mergeCell ref="A30:F30"/>
-    <mergeCell ref="A29:F29"/>
+    <mergeCell ref="A32:G32"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A31:G31"/>
+    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="A35:G35"/>
+    <mergeCell ref="A30:G30"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A29:G29"/>
+    <mergeCell ref="A33:G33"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Teams/generated/MIXED TEAMS 2026 SUMMER - Contact Lists.xlsx
+++ b/Teams/generated/MIXED TEAMS 2026 SUMMER - Contact Lists.xlsx
@@ -501,7 +501,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 02 Apr 2026 11:51</t>
+          <t>Generated 02 Apr 2026 14:17</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 02 Apr 2026 11:51</t>
+          <t>Generated 02 Apr 2026 14:17</t>
         </is>
       </c>
     </row>
@@ -1355,7 +1355,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 02 Apr 2026 11:51</t>
+          <t>Generated 02 Apr 2026 14:17</t>
         </is>
       </c>
     </row>
@@ -1623,7 +1623,7 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>Not Signed Up</t>
+          <t>Senior</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
@@ -1972,7 +1972,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 02 Apr 2026 11:51</t>
+          <t>Generated 02 Apr 2026 14:17</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 02 Apr 2026 11:51</t>
+          <t>Generated 02 Apr 2026 14:17</t>
         </is>
       </c>
     </row>
